--- a/Analysis/rerun_prep/pipeline/work_after/hybrid_ablation_significance.xlsx
+++ b/Analysis/rerun_prep/pipeline/work_after/hybrid_ablation_significance.xlsx
@@ -496,13 +496,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>694</v>
+        <v>994</v>
       </c>
       <c r="F2" t="n">
-        <v>1.29257971633139e-08</v>
+        <v>2.975496070600142e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2065220249835635</v>
+        <v>-0.210913872452334</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         <v>195</v>
       </c>
       <c r="J2" t="n">
-        <v>6.462898581656947e-08</v>
+        <v>1.785297642360085e-08</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>461.5</v>
+        <v>617</v>
       </c>
       <c r="F3" t="n">
-        <v>7.979790106967753e-06</v>
+        <v>1.107791535731154e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1235765943458251</v>
+        <v>-0.1350164365548981</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
         <v>195</v>
       </c>
       <c r="J3" t="n">
-        <v>7.979790106967753e-06</v>
+        <v>1.107791535731154e-06</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2674</v>
+        <v>2903</v>
       </c>
       <c r="F4" t="n">
-        <v>2.778407752085768e-18</v>
+        <v>3.458496239816417e-17</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4828928336620644</v>
+        <v>0.4827876397107166</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         <v>195</v>
       </c>
       <c r="J4" t="n">
-        <v>2.778407752085768e-17</v>
+        <v>3.804345863798059e-16</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>333</v>
+        <v>443</v>
       </c>
       <c r="F5" t="n">
-        <v>3.140603986686292e-09</v>
+        <v>2.599936497432379e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2615384615384616</v>
+        <v>-0.2818671926364234</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         <v>195</v>
       </c>
       <c r="J5" t="n">
-        <v>2.198422790680405e-08</v>
+        <v>1.819955548202665e-08</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="F6" t="n">
-        <v>3.800828700291237e-06</v>
+        <v>3.934650205717639e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1704667981591058</v>
+        <v>-0.2133070348454964</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         <v>195</v>
       </c>
       <c r="J6" t="n">
-        <v>1.140248610087371e-05</v>
+        <v>1.967325102858819e-07</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1765</v>
+        <v>1678.5</v>
       </c>
       <c r="F7" t="n">
-        <v>8.888569209925517e-23</v>
+        <v>1.83202267473352e-23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4966995397764629</v>
+        <v>0.5126101249178172</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>195</v>
       </c>
       <c r="J7" t="n">
-        <v>1.066628305191062e-21</v>
+        <v>2.198427209680224e-22</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>402</v>
+        <v>656.5</v>
       </c>
       <c r="F8" t="n">
-        <v>4.982408454948704e-10</v>
+        <v>2.057828201814659e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2176373684769901</v>
+        <v>-0.2208523753852694</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>194</v>
       </c>
       <c r="J8" t="n">
-        <v>3.985926763958963e-09</v>
+        <v>1.646262561451727e-08</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -811,24 +811,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>247.5</v>
+        <v>389.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1.323713885481864e-07</v>
+        <v>1.447621700131072e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1318152832394516</v>
+        <v>-0.1534700818365395</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>194</v>
       </c>
       <c r="J9" t="n">
-        <v>5.294855541927457e-07</v>
+        <v>4.342865100393215e-07</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -856,13 +856,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2527.5</v>
+        <v>2818.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.444333254681302e-18</v>
+        <v>3.783797341061508e-17</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4061802529493039</v>
+        <v>0.4090232755872037</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>194</v>
       </c>
       <c r="J10" t="n">
-        <v>1.588766580149432e-17</v>
+        <v>3.783797341061508e-16</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>479.5</v>
+        <v>764.5</v>
       </c>
       <c r="F11" t="n">
-        <v>6.657833777665511e-09</v>
+        <v>4.223450911919335e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1947140039447732</v>
+        <v>-0.1933990795529257</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>195</v>
       </c>
       <c r="J11" t="n">
-        <v>3.994700266599307e-08</v>
+        <v>1.689380364767734e-07</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>267</v>
+        <v>378</v>
       </c>
       <c r="F12" t="n">
-        <v>3.882321239590474e-06</v>
+        <v>5.251971513174312e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1055358316896778</v>
+        <v>-0.135568704799474</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>195</v>
       </c>
       <c r="J12" t="n">
-        <v>7.764642479180948e-06</v>
+        <v>1.050394302634862e-06</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3549.5</v>
+        <v>3437</v>
       </c>
       <c r="F13" t="n">
-        <v>2.726975529748005e-14</v>
+        <v>8.957683522955028e-15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3368047337278107</v>
+        <v>0.3417225509533202</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>195</v>
       </c>
       <c r="J13" t="n">
-        <v>2.454277976773204e-13</v>
+        <v>8.061915170659526e-14</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1082,22 +1082,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6410256410220513</v>
+        <v>0.5897435897389743</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5591302738537463</v>
+        <v>0.5825917645770494</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7589743589743589</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="F2" t="n">
-        <v>0.428806752859504</v>
+        <v>0.4583065981196316</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1327393162394872</v>
+        <v>0.1363418803415385</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1206929199294017</v>
+        <v>0.119544740341475</v>
       </c>
     </row>
     <row r="3">
@@ -1112,22 +1112,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8974358974364102</v>
+        <v>0.8649572649579488</v>
       </c>
       <c r="D3" t="n">
-        <v>0.28148117231144</v>
+        <v>0.2989432244235501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9076923076923077</v>
+        <v>0.8787179487179487</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2610294996409246</v>
+        <v>0.2831539915374769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04488888888717949</v>
+        <v>0.04851773504205129</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03917388127541459</v>
+        <v>0.0392713156561879</v>
       </c>
     </row>
     <row r="4">
@@ -1142,22 +1142,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6410256410220513</v>
+        <v>0.5897435897389743</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5591302738537463</v>
+        <v>0.5825917645770494</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7589743589743589</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="F4" t="n">
-        <v>0.428806752859504</v>
+        <v>0.4583065981196316</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1327393162394872</v>
+        <v>0.1363418803415385</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1206929199294017</v>
+        <v>0.119544740341475</v>
       </c>
     </row>
     <row r="5">
@@ -1172,22 +1172,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.919999999997436</v>
+        <v>0.8919658119625641</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2636947800038577</v>
+        <v>0.297831719395999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9312820512820512</v>
+        <v>0.9189743589743589</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2511743499197843</v>
+        <v>0.2690168705838659</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04768290598410257</v>
+        <v>0.04829024216666666</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04810872260735358</v>
+        <v>0.04560118072959191</v>
       </c>
     </row>
     <row r="6">
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6410256410220513</v>
+        <v>0.5897435897389743</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5591302738537463</v>
+        <v>0.5825917645770494</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7589743589743589</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="F6" t="n">
-        <v>0.428806752859504</v>
+        <v>0.4583065981196316</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1327393162394872</v>
+        <v>0.1363418803415385</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1206929199294017</v>
+        <v>0.119544740341475</v>
       </c>
     </row>
     <row r="7">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9038373424974226</v>
+        <v>0.8600229095072166</v>
       </c>
       <c r="D7" t="n">
-        <v>0.237464943631205</v>
+        <v>0.3028306711491952</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9193298969072164</v>
+        <v>0.8859106529211341</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2261414671018885</v>
+        <v>0.2743898890342291</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05243091351855671</v>
+        <v>0.0547966065314433</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04467420984266796</v>
+        <v>0.04015272231316915</v>
       </c>
     </row>
     <row r="8">
@@ -1262,22 +1262,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6410256410220513</v>
+        <v>0.5897435897389743</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5591302738537463</v>
+        <v>0.5825917645770494</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7589743589743589</v>
+        <v>0.7025641025641025</v>
       </c>
       <c r="F8" t="n">
-        <v>0.428806752859504</v>
+        <v>0.4583065981196316</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1327393162394872</v>
+        <v>0.1363418803415385</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1206929199294017</v>
+        <v>0.119544740341475</v>
       </c>
     </row>
     <row r="9">
@@ -1292,22 +1292,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8793162393158974</v>
+        <v>0.8326495726502564</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3234259436998544</v>
+        <v>0.358451534477922</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8964102564102565</v>
+        <v>0.8684615384615384</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2749647323166649</v>
+        <v>0.3011878413567289</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07175705128307693</v>
+        <v>0.07399957264871795</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07850185313316729</v>
+        <v>0.07701016228455954</v>
       </c>
     </row>
   </sheetData>
